--- a/testdata/fixtures/members_email_space.xlsx
+++ b/testdata/fixtures/members_email_space.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Liste des membres Club de plongée d'exemple</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t xml:space="preserve">Année(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organisation</t>
   </si>
   <si>
     <t xml:space="preserve">Mme</t>
@@ -209,55 +212,58 @@
       <c r="W4" t="s">
         <v>20</v>
       </c>
+      <c r="X4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" t="s">
+        <v>33</v>
+      </c>
+      <c r="S5" t="s">
+        <v>34</v>
+      </c>
+      <c r="U5" t="s">
         <v>31</v>
       </c>
-      <c r="R5" t="s">
-        <v>32</v>
-      </c>
-      <c r="S5" t="s">
-        <v>33</v>
-      </c>
-      <c r="U5" t="s">
-        <v>30</v>
-      </c>
       <c r="V5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W5">
         <v>2026</v>
@@ -268,49 +274,49 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" t="s">
+        <v>34</v>
+      </c>
+      <c r="U6" t="s">
+        <v>31</v>
+      </c>
+      <c r="V6" t="s">
         <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S6" t="s">
-        <v>33</v>
-      </c>
-      <c r="U6" t="s">
-        <v>30</v>
-      </c>
-      <c r="V6" t="s">
-        <v>34</v>
       </c>
       <c r="W6">
         <v>2026</v>
